--- a/results/emp008_runs/origin_emp008/comparison/performance.xlsx
+++ b/results/emp008_runs/origin_emp008/comparison/performance.xlsx
@@ -506,7 +506,7 @@
         <v>-24.12939214359774</v>
       </c>
       <c r="F2" t="n">
-        <v>351.0874044576111</v>
+        <v>351.087404457611</v>
       </c>
       <c r="G2" t="n">
         <v>9.942751291633479</v>
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.74087520773517</v>
+        <v>57.7346726626965</v>
       </c>
       <c r="C3" t="n">
-        <v>27.50290107951521</v>
+        <v>27.50299687085966</v>
       </c>
       <c r="D3" t="n">
-        <v>1.796322486476154</v>
+        <v>1.796173939153325</v>
       </c>
       <c r="E3" t="n">
         <v>-24.24241953088453</v>
       </c>
       <c r="F3" t="n">
-        <v>348.7032584606245</v>
+        <v>348.6451495316391</v>
       </c>
       <c r="G3" t="n">
         <v>9.943028261636771</v>
@@ -649,13 +649,13 @@
         <v>1.361364131551558</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8207317688842365</v>
+        <v>0.820731768884232</v>
       </c>
       <c r="E2" t="n">
         <v>-1.351280161793711</v>
       </c>
       <c r="F2" t="n">
-        <v>3.717131361416359</v>
+        <v>3.717131361416337</v>
       </c>
       <c r="G2" t="n">
         <v>2.016224039853232</v>
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.952928506389461</v>
+        <v>0.9489781477716397</v>
       </c>
       <c r="C3" t="n">
-        <v>1.361363631049689</v>
+        <v>1.361354110965276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7034269090620758</v>
+        <v>0.7005571724565336</v>
       </c>
       <c r="E3" t="n">
         <v>-1.500670971955376</v>
       </c>
       <c r="F3" t="n">
-        <v>3.17305488375863</v>
+        <v>3.15975824245045</v>
       </c>
       <c r="G3" t="n">
         <v>2.016224039853232</v>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>371.7131361416359</v>
+        <v>371.7131361416337</v>
       </c>
       <c r="C2" t="n">
         <v>111.4267458486595</v>
       </c>
       <c r="D2" t="n">
-        <v>8.770386778952208</v>
+        <v>8.770386778952155</v>
       </c>
       <c r="E2" t="n">
         <v>2.673695182829894</v>
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>317.305488375863</v>
+        <v>315.975824245045</v>
       </c>
       <c r="C3" t="n">
-        <v>95.29285063894611</v>
+        <v>94.89781477716397</v>
       </c>
       <c r="D3" t="n">
-        <v>7.517992131908064</v>
+        <v>7.487142902616291</v>
       </c>
       <c r="E3" t="n">
         <v>1.395953045405518</v>
@@ -821,10 +821,10 @@
         <v>54.76190476190477</v>
       </c>
       <c r="I3" t="n">
-        <v>136.1363631049689</v>
+        <v>136.1354110965275</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6999808755392554</v>
+        <v>0.6970839843417093</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,6 +1563,23 @@
       </c>
       <c r="E42" t="n">
         <v>6.165569602969297</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.1358875526054735</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.06794377630273676</v>
+      </c>
+      <c r="D43" t="n">
+        <v>13.58875526054735</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.794377630273677</v>
       </c>
     </row>
   </sheetData>
@@ -13212,10 +13229,10 @@
         <v>46170</v>
       </c>
       <c r="B831" t="n">
-        <v>-0.0047077471126915</v>
+        <v>-0.0047077471126917</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.0047072203967176</v>
+        <v>-0.0048361149308201</v>
       </c>
       <c r="D831" t="n">
         <v>-0.00484270822105537</v>
@@ -24868,10 +24885,10 @@
         <v>46170</v>
       </c>
       <c r="B831" t="n">
-        <v>3.510874044576111</v>
+        <v>3.51087404457611</v>
       </c>
       <c r="C831" t="n">
-        <v>3.487032584606244</v>
+        <v>3.486451495316391</v>
       </c>
       <c r="D831" t="n">
         <v>3.350769127200514</v>
@@ -36524,10 +36541,10 @@
         <v>46170</v>
       </c>
       <c r="B831" t="n">
-        <v>-0.004707747112691396</v>
+        <v>-0.004707747112691618</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.004707220396717671</v>
+        <v>-0.004836114930820146</v>
       </c>
       <c r="D831" t="n">
         <v>-0.00484270822105537</v>
@@ -37148,10 +37165,10 @@
         <v>46173</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3093356610479292</v>
+        <v>0.309335661047929</v>
       </c>
       <c r="C43" t="n">
-        <v>0.309361773569568</v>
+        <v>0.3091922058009327</v>
       </c>
       <c r="D43" t="n">
         <v>0.3027969561054278</v>
@@ -46312,10 +46329,10 @@
         <v>46170</v>
       </c>
       <c r="B831" t="n">
-        <v>0.0001349611083638694</v>
+        <v>0.0001349611083636699</v>
       </c>
       <c r="C831" t="n">
-        <v>0.0001354878243377692</v>
+        <v>6.593290235269895e-06</v>
       </c>
     </row>
   </sheetData>
@@ -55473,10 +55490,10 @@
         <v>46170</v>
       </c>
       <c r="B831" t="n">
-        <v>0.03717131361416359</v>
+        <v>0.03717131361416337</v>
       </c>
       <c r="C831" t="n">
-        <v>0.0317305488375863</v>
+        <v>0.0315975824245045</v>
       </c>
     </row>
   </sheetData>
@@ -65127,10 +65144,10 @@
         <v>46173</v>
       </c>
       <c r="B43" t="n">
-        <v>0.005329954697538941</v>
+        <v>0.005329954697538719</v>
       </c>
       <c r="C43" t="n">
-        <v>0.005351535243002914</v>
+        <v>0.005221968479977468</v>
       </c>
     </row>
   </sheetData>
